--- a/tests/systeem_testen/224/results/df_beta_uittredepunten.xlsx
+++ b/tests/systeem_testen/224/results/df_beta_uittredepunten.xlsx
@@ -461,10 +461,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>9.839010769011201</v>
+        <v>27.89052457157127</v>
       </c>
       <c r="E2" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.738223270312046e-171</v>
       </c>
     </row>
     <row r="3">
@@ -478,10 +478,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9.839010769011201</v>
+        <v>27.41269549607981</v>
       </c>
       <c r="E3" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.678598680257558e-166</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9.839010769011201</v>
+        <v>16.95750041242504</v>
       </c>
       <c r="E4" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.469947485489923e-65</v>
       </c>
     </row>
     <row r="5">
@@ -512,10 +512,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>9.839010769011201</v>
+        <v>14.27481990390891</v>
       </c>
       <c r="E5" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.570490951438946e-46</v>
       </c>
     </row>
     <row r="6">
@@ -529,10 +529,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>9.839010769011201</v>
+        <v>26.23298002375888</v>
       </c>
       <c r="E6" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.589611861524541e-152</v>
       </c>
     </row>
     <row r="7">
@@ -546,10 +546,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>9.839010769011201</v>
+        <v>27.1214525927446</v>
       </c>
       <c r="E7" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.749918415221198e-162</v>
       </c>
     </row>
     <row r="8">
@@ -563,10 +563,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>9.839010769011201</v>
+        <v>27.15692788534682</v>
       </c>
       <c r="E8" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.048642943733701e-162</v>
       </c>
     </row>
     <row r="9">
@@ -580,10 +580,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>9.839010769011201</v>
+        <v>17.28063040141005</v>
       </c>
       <c r="E9" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.291231350136076e-67</v>
       </c>
     </row>
     <row r="10">
@@ -597,10 +597,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>9.839010769011201</v>
+        <v>26.40191882151398</v>
       </c>
       <c r="E10" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.511962590025216e-154</v>
       </c>
     </row>
     <row r="11">
@@ -614,10 +614,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>9.839010769011201</v>
+        <v>28.07351201861387</v>
       </c>
       <c r="E11" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.031643010433468e-173</v>
       </c>
     </row>
     <row r="12">
@@ -631,10 +631,10 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>9.839010769011201</v>
+        <v>27.92555283567018</v>
       </c>
       <c r="E12" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.531433836387407e-172</v>
       </c>
     </row>
     <row r="13">
@@ -648,10 +648,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>9.839010769011201</v>
+        <v>26.65028511038638</v>
       </c>
       <c r="E13" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.880607156402828e-157</v>
       </c>
     </row>
     <row r="14">
@@ -665,10 +665,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>9.839010769011201</v>
+        <v>27.10855895475426</v>
       </c>
       <c r="E14" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.90265286812219e-162</v>
       </c>
     </row>
     <row r="15">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>9.839010769011201</v>
+        <v>27.16127510592883</v>
       </c>
       <c r="E15" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.317140309120556e-163</v>
       </c>
     </row>
     <row r="16">
@@ -699,10 +699,10 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>9.839010769011201</v>
+        <v>25.89786440562139</v>
       </c>
       <c r="E16" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.519499775138432e-148</v>
       </c>
     </row>
     <row r="17">
@@ -716,10 +716,10 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>9.839010769011201</v>
+        <v>25.67790619042865</v>
       </c>
       <c r="E17" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.031820710408866e-145</v>
       </c>
     </row>
     <row r="18">
@@ -733,10 +733,10 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>9.839010769011201</v>
+        <v>25.83141940743442</v>
       </c>
       <c r="E18" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.967711496830981e-147</v>
       </c>
     </row>
     <row r="19">
@@ -750,10 +750,10 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>9.839010769011201</v>
+        <v>25.32512745890356</v>
       </c>
       <c r="E19" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.446515874180643e-142</v>
       </c>
     </row>
     <row r="20">
@@ -767,10 +767,10 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>9.839010769011201</v>
+        <v>13.96318348866526</v>
       </c>
       <c r="E20" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.307438727690809e-44</v>
       </c>
     </row>
     <row r="21">
@@ -784,10 +784,10 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>9.839010769011201</v>
+        <v>13.91953628013584</v>
       </c>
       <c r="E21" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.410106294400354e-44</v>
       </c>
     </row>
     <row r="22">
@@ -801,10 +801,10 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>9.839010769011201</v>
+        <v>14.88476590516607</v>
       </c>
       <c r="E22" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.069663694866074e-50</v>
       </c>
     </row>
     <row r="23">
@@ -818,10 +818,10 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>9.839010769011201</v>
+        <v>23.01220457691642</v>
       </c>
       <c r="E23" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.759154632781997e-117</v>
       </c>
     </row>
     <row r="24">
@@ -835,10 +835,10 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>9.839010769011201</v>
+        <v>26.62248073812537</v>
       </c>
       <c r="E24" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.864389528898285e-156</v>
       </c>
     </row>
     <row r="25">
@@ -852,10 +852,10 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>9.839010769011201</v>
+        <v>33.47904123895613</v>
       </c>
       <c r="E25" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.865081137474357e-246</v>
       </c>
     </row>
     <row r="26">
@@ -869,10 +869,10 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>9.839010769011201</v>
+        <v>14.84350142134009</v>
       </c>
       <c r="E26" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.832427691087692e-50</v>
       </c>
     </row>
     <row r="27">
@@ -886,10 +886,10 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>9.839010769011201</v>
+        <v>14.3672289982622</v>
       </c>
       <c r="E27" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.15448804624222e-47</v>
       </c>
     </row>
     <row r="28">
@@ -903,10 +903,10 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>9.839010769011201</v>
+        <v>14.12568286102768</v>
       </c>
       <c r="E28" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.319149914024955e-45</v>
       </c>
     </row>
     <row r="29">
@@ -920,10 +920,10 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>9.839010769011201</v>
+        <v>14.30464411827046</v>
       </c>
       <c r="E29" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.023410930530316e-46</v>
       </c>
     </row>
     <row r="30">
@@ -937,10 +937,10 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>9.839010769011201</v>
+        <v>13.282481226944</v>
       </c>
       <c r="E30" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.46268743978562e-40</v>
       </c>
     </row>
     <row r="31">
@@ -954,10 +954,10 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>9.839010769011201</v>
+        <v>13.36019126533477</v>
       </c>
       <c r="E31" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.164919137477e-41</v>
       </c>
     </row>
     <row r="32">
@@ -971,10 +971,10 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>9.839010769011201</v>
+        <v>14.09009060038114</v>
       </c>
       <c r="E32" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.185003069200744e-45</v>
       </c>
     </row>
     <row r="33">
@@ -988,10 +988,10 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>9.839010769011201</v>
+        <v>15.44473304407364</v>
       </c>
       <c r="E33" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.093293593845343e-54</v>
       </c>
     </row>
     <row r="34">
@@ -1005,10 +1005,10 @@
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>9.839010769011201</v>
+        <v>13.76054391115758</v>
       </c>
       <c r="E34" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.201012675825945e-43</v>
       </c>
     </row>
     <row r="35">
@@ -1022,10 +1022,10 @@
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>9.839010769011201</v>
+        <v>13.39041489308758</v>
       </c>
       <c r="E35" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.439768555147069e-41</v>
       </c>
     </row>
     <row r="36">
@@ -1039,10 +1039,10 @@
         <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>9.839010769011201</v>
+        <v>14.03703866829834</v>
       </c>
       <c r="E36" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.624885406802116e-45</v>
       </c>
     </row>
     <row r="37">
@@ -1056,10 +1056,10 @@
         <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>9.839010769011201</v>
+        <v>29.21713290880512</v>
       </c>
       <c r="E37" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.875010938387574e-188</v>
       </c>
     </row>
     <row r="38">
@@ -1073,10 +1073,10 @@
         <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>9.839010769011201</v>
+        <v>13.97663180852043</v>
       </c>
       <c r="E38" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.08246973878258e-44</v>
       </c>
     </row>
     <row r="39">
@@ -1090,10 +1090,10 @@
         <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>9.839010769011201</v>
+        <v>13.43904699133769</v>
       </c>
       <c r="E39" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.785023554972823e-41</v>
       </c>
     </row>
     <row r="40">
@@ -1107,10 +1107,10 @@
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>9.839010769011201</v>
+        <v>13.48803796005611</v>
       </c>
       <c r="E40" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.196518685386608e-42</v>
       </c>
     </row>
     <row r="41">
@@ -1124,10 +1124,10 @@
         <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>9.839010769011201</v>
+        <v>14.05122371302614</v>
       </c>
       <c r="E41" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.785715567044263e-45</v>
       </c>
     </row>
     <row r="42">
@@ -1141,10 +1141,10 @@
         <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>9.839010769011201</v>
+        <v>29.92385788624454</v>
       </c>
       <c r="E42" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.815884050377117e-197</v>
       </c>
     </row>
     <row r="43">
@@ -1158,10 +1158,10 @@
         <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>9.839010769011201</v>
+        <v>13.68342042517644</v>
       </c>
       <c r="E43" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.377441099677514e-43</v>
       </c>
     </row>
     <row r="44">
@@ -1175,10 +1175,10 @@
         <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>9.839010769011201</v>
+        <v>13.65902978704865</v>
       </c>
       <c r="E44" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.917202945310766e-43</v>
       </c>
     </row>
     <row r="45">
@@ -1192,10 +1192,10 @@
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>9.839010769011201</v>
+        <v>13.9496038761676</v>
       </c>
       <c r="E45" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.581787807705562e-44</v>
       </c>
     </row>
     <row r="46">
@@ -1209,10 +1209,10 @@
         <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>9.839010769011201</v>
+        <v>13.89648347257791</v>
       </c>
       <c r="E46" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.326532056127628e-44</v>
       </c>
     </row>
     <row r="47">
@@ -1226,10 +1226,10 @@
         <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>9.839010769011201</v>
+        <v>13.85491975102566</v>
       </c>
       <c r="E47" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.939477887627076e-44</v>
       </c>
     </row>
     <row r="48">
@@ -1243,10 +1243,10 @@
         <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>9.839010769011201</v>
+        <v>13.4611477020265</v>
       </c>
       <c r="E48" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.32385696672101e-41</v>
       </c>
     </row>
     <row r="49">
@@ -1260,10 +1260,10 @@
         <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>9.839010769011201</v>
+        <v>13.72746546431227</v>
       </c>
       <c r="E49" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.476165481344158e-43</v>
       </c>
     </row>
     <row r="50">
@@ -1277,10 +1277,10 @@
         <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>9.839010769011201</v>
+        <v>13.58768839872289</v>
       </c>
       <c r="E50" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.369048323327631e-42</v>
       </c>
     </row>
     <row r="51">
@@ -1294,10 +1294,10 @@
         <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>9.839010769011201</v>
+        <v>13.45281484550868</v>
       </c>
       <c r="E51" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.481858553203805e-41</v>
       </c>
     </row>
     <row r="52">
@@ -1311,10 +1311,10 @@
         <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>9.839010769011201</v>
+        <v>28.86214364003889</v>
       </c>
       <c r="E52" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.783785948189318e-183</v>
       </c>
     </row>
     <row r="53">
@@ -1328,10 +1328,10 @@
         <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>9.839010769011201</v>
+        <v>24.42863022210409</v>
       </c>
       <c r="E53" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.245594704333063e-132</v>
       </c>
     </row>
     <row r="54">
@@ -1345,10 +1345,10 @@
         <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>9.839010769011201</v>
+        <v>23.62908882821463</v>
       </c>
       <c r="E54" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.683582716932677e-124</v>
       </c>
     </row>
     <row r="55">
@@ -1362,10 +1362,10 @@
         <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>9.839010769011201</v>
+        <v>28.74547228827583</v>
       </c>
       <c r="E55" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.159156067528768e-182</v>
       </c>
     </row>
     <row r="56">
@@ -1379,10 +1379,10 @@
         <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>9.839010769011201</v>
+        <v>22.45000197204704</v>
       </c>
       <c r="E56" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.398301328113765e-112</v>
       </c>
     </row>
     <row r="57">
@@ -1396,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>9.839010769011201</v>
+        <v>21.31598945420247</v>
       </c>
       <c r="E57" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.034193157535672e-101</v>
       </c>
     </row>
     <row r="58">
@@ -1413,10 +1413,10 @@
         <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>9.839010769011201</v>
+        <v>19.24216060631383</v>
       </c>
       <c r="E58" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.210922229258382e-83</v>
       </c>
     </row>
     <row r="59">
@@ -1430,10 +1430,10 @@
         <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>9.839010769011201</v>
+        <v>21.17776007911912</v>
       </c>
       <c r="E59" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>7.657157496743284e-100</v>
       </c>
     </row>
   </sheetData>
